--- a/Summary of data by cose and income with IF.xlsx
+++ b/Summary of data by cose and income with IF.xlsx
@@ -33,13 +33,13 @@
     <t xml:space="preserve">World_bank_classification</t>
   </si>
   <si>
+    <t xml:space="preserve">    .lower_middle_income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .upper_middle_income</t>
+  </si>
+  <si>
     <t xml:space="preserve">    high_income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    lower_middle_income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    upper_middle_income</t>
   </si>
   <si>
     <t xml:space="preserve">Impact_Factor_Index</t>
@@ -67,13 +67,13 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">469 (88%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">14 (2.6%)</t>
   </si>
   <si>
     <t xml:space="preserve">49 (9.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">471 (88%)</t>
   </si>
   <si>
     <t xml:space="preserve">2.6 (1.7, 4.1)</t>
@@ -593,88 +593,80 @@
     </row>
     <row r="9" ht="NA" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>20</v>
+        <v>4</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>142</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="NA" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="13" ht="NA" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>151</v>
+        <v>11</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" ht="NA" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>22</v>
+        <v>4</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>139</v>
       </c>
     </row>
     <row r="15" ht="NA" customHeight="1">
       <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" ht="NA" customHeight="1">
+      <c r="A16" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="9" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" ht="NA" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" ht="NA" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="10" t="n">
+      <c r="B16" s="10" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="s">
+    <row r="17">
+      <c r="A17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B17" s="6" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
